--- a/output/pdf_financials_xlsx/NUE.xlsx
+++ b/output/pdf_financials_xlsx/NUE.xlsx
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.235657</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.237497</v>
       </c>
     </row>
     <row r="93">
@@ -2936,7 +2936,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>2.235657</v>
       </c>

--- a/output/pdf_financials_xlsx/NUE.xlsx
+++ b/output/pdf_financials_xlsx/NUE.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.048228</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.7553840000000001</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.048228</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.7553840000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.09722699999999999</v>
+        <v>0.048999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.74605</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/NUE.xlsx
+++ b/output/pdf_financials_xlsx/NUE.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -471,39 +471,43 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.5665829999999999</v>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.031645</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-0.02073</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.5665829999999999</v>
+          <t>Net Interest Income (for Banks)</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
@@ -514,98 +518,114 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>1.847708</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1.161329</v>
+          <t>Non Interest Income</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Research &amp; Development</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>0.5665829999999999</v>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Operating Expense</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
+          <t>Credit Losses Provision</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Operating Expense</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>4.018086</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>2.66827</v>
+          <t>Total Noninterest Expense</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-3.451503</v>
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.66827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Interest Income</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.5665829999999999</v>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Interest Expense</t>
+          <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>2.775208</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>1.823079</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Interest Income</t>
+          <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -618,7 +638,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Income (Expense)</t>
+          <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -631,80 +651,72 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Pretax Income</t>
+          <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3.669462</v>
+        <v>4.018086</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-8.44749</v>
+        <v>2.66827</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tax Provision</t>
+          <t>Operating Income</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.451503</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.66827</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Net Income (Loss)</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">    Interest Income</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Income Including Noncontrolling Interests</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">    Interest Expense</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Net Income (Continuing Operations)</t>
+          <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-3.669462</v>
+        <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-8.44749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
+          <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
@@ -717,434 +729,474 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Income (Minority Interest)</t>
+          <t>Pretax Income</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0</v>
+        <v>-3.662155</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>-8.44749</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-3.669462</v>
+        <v>-0.007307</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-8.44749</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>EPS (Basic)</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>-0.19</v>
+          <t xml:space="preserve">  Other Net Income (Loss)</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>EPS (Diluted)</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>-0.19</v>
+          <t xml:space="preserve">  Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Shares Outstanding (Diluted Average)</t>
+          <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>30.57885</v>
+        <v>-3.669462</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>44.460474</v>
+        <v>-8.44749</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.669462</v>
+        <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.44749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
+          <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.06959899999999999</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.41131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.599863</v>
+        <v>-3.669462</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.03618</v>
+        <v>-8.44749</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EBITDA Margin %</t>
+          <t>EPS (Basic)</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-635.3637507655543</v>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.12</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Tax Rate %</t>
+          <t>EPS (Diluted)</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.12</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Net Margin %</t>
+          <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-647.647740931161</v>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>30.57885</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>44.460474</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Balance Sheet</t>
-        </is>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>-3.662155</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>-8.44749</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Cash and Cash Equivalents</t>
+          <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.048228</v>
+        <v>0.06959899999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.7553840000000001</v>
+        <v>0.41131</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Marketable Securities</t>
+          <t>EBITDA</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>-3.592556</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>-8.03618</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
+          <t>EBITDA Margin %</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.048228</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>0.7553840000000001</v>
+        <v>-634.0740897626649</v>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Accounts Receivable</t>
+          <t>Tax Rate %</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.180695</v>
+        <v>-0.1995273274888693</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.164741</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Notes Receivable</t>
+          <t>Net Margin %</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>0</v>
+        <v>-647.647740931161</v>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Loans Receivable</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>0.003642</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>0.176814</v>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Other Current Receivables</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>0</v>
+          <t>Balance Statement Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Receivables</t>
+          <t>Money Market Investments</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.184337</v>
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.341555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>0</v>
+          <t>Gross Loan</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Inventories, Work In Process</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>0</v>
+          <t>Allowance For Loans And Lease Losses</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>0</v>
+          <t>Net Loan</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Inventories, Finished Goods</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>0</v>
+          <t>Securities &amp; Investments</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Inventories, Other</t>
+          <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>0.048228</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0</v>
+        <v>0.7553840000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Inventories</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>0.513059</v>
+          <t xml:space="preserve">    Marketable Securities</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Current Assets</t>
+          <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.048999</v>
+        <v>0.048228</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>0.7553840000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Current Assets</t>
+          <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0.281564</v>
+        <v>0.180695</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1.600664</v>
+        <v>0.164741</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Investments And Advances</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Notes Receivable</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Land And Improvements</t>
+          <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>0</v>
+        <v>0.003642</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0</v>
+        <v>0.176814</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Buildings And Improvements</t>
+          <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>0</v>
+        <v>0.015771</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0</v>
+        <v>0.0083</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
+          <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0.008987999999999999</v>
+        <v>0.200108</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0.031775</v>
+        <v>0.349855</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Construction In Progress</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Other Gross PPE</t>
+          <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
@@ -1161,560 +1213,664 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Accumulated Depreciation</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Inventories, Finished Goods</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Property, Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>0.088203</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>0.344043</v>
+          <t xml:space="preserve">    Inventories, Other</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Total Inventories</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>2.114174</v>
+        <v>0.513059</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Goodwill</t>
+          <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>0</v>
+        <v>0.033228</v>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Long Term Assets</t>
+          <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>0.185802</v>
+        <v>0.281564</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.208589</v>
+        <v>1.600664</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Long-Term Assets</t>
+          <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>0.274005</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>2.666806</v>
+        <v>0.137509</v>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>0.555569</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>4.26747</v>
+          <t xml:space="preserve">      Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Accounts Payable</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>1.843906</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>2.725149</v>
+          <t xml:space="preserve">      Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Total Tax Payable</t>
+          <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>0</v>
+        <v>0.008987999999999999</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0</v>
+        <v>0.031775</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Other Current Payables</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">      Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Current Accrued Expense</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">      Other Gross PPE</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>1.843906</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>2.725149</v>
+          <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Short-Term Debt</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
+          <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.088203</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.344043</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>2.114174</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Current Deferred Revenue</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Goodwill</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
+          <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>0</v>
+        <v>0.235956</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>0</v>
+        <v>0.208589</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Deferred Tax And Revenue</t>
+          <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>0</v>
+        <v>0.461668</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0</v>
+        <v>2.666806</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Current Liabilities</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.619452</v>
+        <v>0.555569</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1.355362</v>
+        <v>4.26747</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Current Liabilities</t>
+          <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>2.463358</v>
+        <v>1.843906</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>4.080511</v>
+        <v>2.725149</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Long-Term Debt</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="n">
-        <v>0.057515</v>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>0.267328</v>
+          <t xml:space="preserve">    Other Current Payables</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
+          <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0.057515</v>
+        <v>0.099508</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0.267328</v>
+        <v>0.295029</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Debt-to-Equity</t>
+          <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>-0.02926519256054025</v>
+        <v>-0.047883</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>-3.326257636650948</v>
+        <v>3.020178</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Pension And Retirement Benefit</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Short-Term Debt</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
+          <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>0</v>
+        <v>0.031672</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0</v>
+        <v>0.082746</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
+          <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>0</v>
+        <v>0.031672</v>
       </c>
       <c r="C83" s="3" t="n">
-        <v>0</v>
+        <v>0.082746</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Long-Term Liabilities</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Long-Term Liabilities</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>0.057515</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>0.267328</v>
+          <t xml:space="preserve">  Deferred Tax And Revenue</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>Total Liabilities</t>
+          <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>2.520873</v>
+        <v>2.479569</v>
       </c>
       <c r="C87" s="3" t="n">
-        <v>4.347839</v>
+        <v>0.977587</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Common Stock</t>
+          <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>10.612913</v>
+        <v>2.463358</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>19.943498</v>
+        <v>4.080511</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Preferred Stock</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">    Long-Term Debt</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Retained Earnings</t>
+          <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>-14.813874</v>
+        <v>0.057515</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>-23.261364</v>
+        <v>0.267328</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
+          <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.057515</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.267328</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Additional Paid-In Capital</t>
+          <t>Debt-to-Equity</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.235657</v>
+        <v>-0.04538076552024521</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>3.237497</v>
+        <v>-4.355833716980428</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Treasury Stock</t>
+          <t>Total Deposits</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>0</v>
+        <v>0.034011</v>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total Stockholders Equity</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>-1.965304</v>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>-0.080369</v>
+          <t>Other Assets for Banks</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Minority Interest</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>0</v>
+          <t>Other Liabilities for Banks</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>-1.965304</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>-0.080369</v>
+          <t xml:space="preserve">  Pension And Retirement Benefit</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>Equity-to-Asset</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>-3.537461593429439</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>-0.01883293848580072</v>
+          <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Cashflow Statement</t>
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Income From Continuing Operations</t>
+          <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
@@ -1731,75 +1887,59 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
-        </is>
-      </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Other Long-Term Liabilities</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Change In Receivables</t>
-        </is>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Total Long-Term Liabilities</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>0.057515</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.267328</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Change In Inventory</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>2.520873</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>4.347839</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Change In Prepaid Assets</t>
-        </is>
-      </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Common Stock</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>10.085997</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>19.943498</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
+          <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
@@ -1816,24 +1956,20 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Change In Other Working Capital</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>-14.813874</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>-23.261364</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Change In Working Capital</t>
+          <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
@@ -1850,24 +1986,20 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stock Based Compensation</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Additional Paid-In Capital</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>2.235657</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>3.237497</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Asset Impairment Charge</t>
+          <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
@@ -1884,24 +2016,20 @@
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Total Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>-1.965304</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>-0.080369</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash Flow from Others</t>
+          <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
@@ -1918,426 +2046,519 @@
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>-1.965304</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>-0.080369</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Equity-to-Asset</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>-3.537461593429439</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>-0.01883293848580072</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Purchase Of Business</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Cashflow Statement</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchase Of Investment</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Net Income From Continuing Operations</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>-3.669462</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>-8.44749</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sale Of Investment</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>0.06959899999999999</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0.41131</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">    Change In Receivables</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>-0.018836</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0.449187</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">    Change In Inventory</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>-0.441221</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash From Other Investing Activities</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">    Change In Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>-0.014988</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0.050892</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>Cash Flow from Investing</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>1.30979</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0.733026</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Issuance of Stock</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">    Change In Other Working Capital</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Repurchase of Stock</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Change In Working Capital</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>-0.01205</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0.791884</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Stock Based Compensation</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>0.567492</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0.017237</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Issuance of Debt</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Asset Impairment Charge</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Payments of Debt</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Issuance of Debt</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Cash Flow from Others</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash Flow for Dividends</t>
-        </is>
-      </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>-0.004867</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash Flow for Lease Financing</t>
-        </is>
-      </c>
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other Financing</t>
-        </is>
-      </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Purchase Of Business</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>Cash Flow from Financing</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Purchase Of Investment</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Beginning Cash Position</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Sale Of Investment</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net Change in Cash</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>Ending Cash Position</t>
-        </is>
-      </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t xml:space="preserve">  Cash From Other Investing Activities</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>Capital Expenditure</t>
-        </is>
-      </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash Flow from Investing</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>0.089363</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0.029526</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Issuance of Stock</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Repurchase of Stock</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Issuance of Debt</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Payments of Debt</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>-0.053386</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>-0.053181</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net Issuance of Debt</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>-0.053386</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>-0.053181</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash Flow for Dividends</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cash Flow for Lease Financing</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Financing</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>-0.003084</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>-0.059134</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Cash Flow from Financing</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>0.72153</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>1.823708</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Beginning Cash Position</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>0.816883</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>0.048228</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net Change in Cash</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>-0.768655</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>0.707156</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>Ending Cash Position</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>0.048228</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>0.7553840000000001</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>Capital Expenditure</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>-0.004867</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B150" s="3" t="n">
+        <v>-1.584415</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>-1.146078</v>
       </c>
     </row>
   </sheetData>
@@ -2351,7 +2572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2800,7 +3021,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.031672</v>
       </c>
@@ -3027,22 +3252,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Revenue 16 $</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Cash $48,228</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>0.5665829999999999</v>
+        <v>0.816883</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3053,322 +3278,340 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Accounting and audit</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Trade and other receivables (note 5) 180,695</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>0.422909</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0.416644</v>
+        <v>0.161859</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Prepaids and deposits (note 6) 48,999</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.335661</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>0.44338</v>
+        <v>0.034011</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 11,12,13</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Loans receivable (note7) 3,642</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>0.06959899999999999</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0.41131</v>
+        <v>0.045983</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Filing and transfer agent fees</t>
+          <t>Total current assets 281,564</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.033828</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.045987</v>
+        <v>1.058736</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Loans receivable (note 7) 176,814</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>LoansReceivable</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.050046</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0.061207</v>
+        <v>0.176814</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Investments (note 8) -</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InvestmentsAndAdvances</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.06866800000000001</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0.01354</v>
+        <v>0.137509</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Right-of-use assets (note 9) 88,203</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.123981</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0.169571</v>
+        <v>0.079663</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Management and director fees 16</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Property, plant and equipment (note 10) 8,988</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
-        <v>0.9275</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>0.6617499999999999</v>
+        <v>0.06768200000000001</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marketing and promotion</t>
+          <t>Total non-current assets 274,005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalNonCurrentAssets</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1.101957</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0.322</v>
+        <v>0.461668</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Total assets $555,569</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
-        <v>0.0604</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>0.029568</v>
+        <v>1.520404</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounts payable and accrued liabilities (note 11) $1,843,906</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" s="5" t="n">
-        <v>0.051058</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0.042334</v>
+        <v>0.534116</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Loans and borrowings (note 12) 587,780</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>0.182878</v>
+        <v>0.3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3379,234 +3622,254 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Share-based payments 19</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Leases (note 9) 31,672</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>0.567492</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.017237</v>
+        <v>0.05128</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Total current liabilities 2,463,358</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.022109</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.033742</v>
+        <v>0.885396</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Leases (note 9) 57,515</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>Leases</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>4.018086</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>2.66827</v>
+        <v>0.025258</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non-current</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Total liabilities 2,520,873</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-3.451503</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>-2.66827</v>
+        <v>0.910654</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finance expense, net 20</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Common shares (note 13) 10,612,913</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CommonStock</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
-        <v>-0.084166</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>-0.081966</v>
+        <v>10.085997</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gain (loss) on sale of equipment</t>
+          <t>Warrants (note 13) 50,491</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>-0.003591</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0.019904</v>
+        <v>1.040491</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 18</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0.08447300000000001</v>
+          <t>Contributed surplus 2,185,166</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.627674</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Acquisition expense 4</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>AcquisitionExpense</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>-5.801631</v>
+          <t>Deficit (14,813,874)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>-11.144412</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Share in loss of joint venture and associate 9</t>
+          <t>Total shareholders’ (deficiency) equity (1,965,304)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>-0.137509</v>
+        <v>0.60975</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3617,46 +3880,48 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Loss before taxes</t>
+          <t>Total liabilities and shareholders’ (deficiency) equity $555,569</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>-3.676769</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>-8.44749</v>
+        <v>1.520404</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Income tax recovery</t>
+          <t>Going concern (note</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>0.007307</v>
+        <v>1e-06</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3667,222 +3932,242 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>SHAREHOLDERS’ EQUITY (DEFICIENCY)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Subsequent events (note</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>-3.669462</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-8.44749</v>
+        <v>2.2e-05</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>transaction</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-1.2e-07</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>-1.9e-07</v>
+        <v>0.06313100000000001</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>transaction</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>30.299073</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>44.151198</v>
+        <v>-0.047883</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20.  NET FINANCE EXPENSE</t>
+          <t>transaction</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Interest on loans and borrowings $</t>
+          <t>transaction total</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>0.07660699999999999</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0.08368200000000001</v>
+        <v>0.015248</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20.  NET FINANCE EXPENSE</t>
+          <t>5.  Trade and other receivables</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Interest on lease liabilities (Note 11)</t>
+          <t>Trade receivables $142,281</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>0.007609</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.012507</v>
+        <v>0.146088</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20.  NET FINANCE EXPENSE</t>
+          <t>5.  Trade and other receivables</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bank fees and other</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Other receivables 38,414</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
-        <v>0.031595</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0.006507</v>
+        <v>0.015771</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20.  NET FINANCE EXPENSE</t>
+          <t>5.  Trade and other receivables</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Interest revenue (Note 10)</t>
+          <t>5.  Trade and other receivables total</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>-0.031645</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>-0.02073</v>
+        <v>0.161859</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20.  NET FINANCE EXPENSE</t>
+          <t>6.  Prepaids and deposits</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>20.  NET FINANCE EXPENSE total</t>
+          <t>Prepaids $32,167</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="n">
-        <v>0.084166</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.081966</v>
+        <v>0.028002</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6.  Prepaids and deposits</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Revenue (note 14) $566,583</t>
+          <t>Security deposit 16,832</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.401364</v>
+        <v>0.006009</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3893,26 +4178,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>6.  Prepaids and deposits</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>General and administrative (note 15) 3,380,995</t>
+          <t>6.  Prepaids and deposits total</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>TotalDeposits</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2.569864</v>
+        <v>0.034011</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3923,22 +4208,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 13) 567,492</t>
+          <t>At December 31, 2022</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.459197</v>
+        <v>0.09693599999999999</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3949,26 +4234,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Depreciation and amortization (notes 9, 10) 69,599</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>0.087659</v>
+        <v>0.425145</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3979,22 +4260,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Share in loss of joint venture and associate (note 8) 137,509</t>
+          <t>Payments of principal</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>0.006241</v>
+        <v>-0.299284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4005,22 +4286,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Operating loss (3,589,012)</t>
+          <t>At December 31, 2023</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>-2.721597</v>
+        <v>0.222797</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4031,22 +4312,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reverse takeover expense (note 4) -</t>
+          <t>At December 31, 2024</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>-6.436937</v>
+        <v>0.180456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4057,22 +4338,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>(Loss) gain on sale of assets (note 10) (3,591)</t>
+          <t>interest are received  if there is excess cash after the LC NU-Energy joint venture sells a ready-to-build development project. During the year ended December 31, 2024, the Company recognized</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.223604</v>
+        <v>0.022264</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4083,22 +4364,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>note.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Finance expense, net (note 17) (84,166)</t>
+          <t>ended December 31, 2024, the Company recognized $9,110 (2023 - $4,762) of interest income related to the payment plan in finance expense, net. At December 31, 2024, $3,642 (December 31, 2023 -</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>-0.035018</v>
+        <v>0.045983</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4109,22 +4390,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>amount of loan receivable has been repaid.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Loss before income tax (3,676,769)</t>
+          <t>Loans receivable $180,456</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>-8.969948</v>
+        <v>0.222797</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4135,22 +4416,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>amount of loan receivable has been repaid.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Income tax recovery (note 16) 7,307</t>
+          <t>Less: current portion 3,642</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>0.02461</v>
+        <v>0.045983</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4161,22 +4442,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>amount of loan receivable has been repaid.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss ($3,669,462)</t>
+          <t>amount of loan receivable has been repaid. total</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>-8.945338</v>
+        <v>0.176814</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4187,22 +4468,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>At December 31, 2022                                                          $-               $-               $-</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Net loss per share attributable to shareholders (note</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Equity investment 50 143,750</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EquityInvestments</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
-        <v>1.3e-05</v>
+        <v>0.1438</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4213,22 +4498,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>At December 31, 2022                                                          $-               $-               $-</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Basic and diluted, net loss per share ($0.12)</t>
+          <t>Loss from equity investment (50) (6,241)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>-3.6e-07</v>
+        <v>-0.006291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4239,22 +4524,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+          <t>At December 31, 2022                                                          $-               $-               $-</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2024 $10,085,997 $1,040,491 $627,674 ($11,144,412)</t>
+          <t>At December 31, 2023 - 137,509</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>0.60975</v>
+        <v>0.137509</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4265,22 +4550,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+          <t>At December 31, 2022                                                          $-               $-               $-</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Loss for the period - - - (3,669,462)</t>
+          <t>Loss from equity investment - (137,509)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" s="5" t="n">
-        <v>-3.669462</v>
+        <v>-0.137509</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4291,22 +4576,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+          <t>liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shares issued for services (note 13) 30,000 - - -</t>
+          <t>LC NU-Energy Corp. December 31, 2024 December 31,</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="n">
-        <v>0.03</v>
+        <v>0.002023</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4317,22 +4602,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+          <t>liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Shares issued in private placement, net (note 13) 496,916 - - -</t>
+          <t>Current assets $39,101</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
-        <v>0.496916</v>
+        <v>0.106092</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4343,24 +4628,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+          <t>liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Expiry of warrants (note 13) - (990,000) 990,000 -</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Non-current assets 3,205,831</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentAssets</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>1.775718</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4371,22 +4658,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+          <t>liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 13) - - 567,492 -</t>
+          <t>liabilities, and preferred shares, gross. total</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" s="5" t="n">
-        <v>0.567492</v>
+        <v>1.88181</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4397,22 +4684,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+          <t>liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 $10,612,913 $50,491 $2,185,166 ($14,813,874)</t>
+          <t>Current liabilities $3,230,740</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>-1.965304</v>
+        <v>1.460266</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4423,22 +4710,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Balance, January 1, 2023 $4,578,012 $50,491 $254,277 ($2,199,074)</t>
+          <t>Preference shares $457,742</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>2.683706</v>
+        <v>0.457742</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4449,22 +4736,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>Lethbridge One Solar Corp.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Loss for the period - - - (8,945,338)</t>
+          <t>LOSC commenced construction on its Lethbridge One solar power development in late December</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>-8.945338</v>
+        <v>0.002023</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4475,22 +4762,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>assets, liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Repurchase and cancellation of shares (note 13) (104,200) - (95,800) -</t>
+          <t>Lethbridge One Solar Corp. December 31, 2024 December 31,</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>-0.2</v>
+        <v>0.002023</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4501,22 +4788,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>assets, liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shares and warrants issued pursuant to reverse 5,462,185 990,000 - -</t>
+          <t>Current assets $179,640</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>6.452185</v>
+        <v>2.610699</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4527,22 +4814,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>assets, liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>takeover (note</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Non-current assets 20,051,184</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TotalNonCurrentAssets</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
-        <v>1.3e-05</v>
+        <v>4.632204</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4553,22 +4844,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>assets, liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shares issued for services (note 13) 150,000 - 10,000 -</t>
+          <t>assets, liabilities, and preferred shares, gross. total</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="5" t="n">
-        <v>0.16</v>
+        <v>7.242903</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4579,22 +4870,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>assets, liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 13) - - 459,197 -</t>
+          <t>Current liabilities $14,022,998</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>0.459197</v>
+        <v>6.448512</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4605,24 +4896,3540 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+          <t>assets, liabilities, and preferred shares, gross.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 $10,085,997 $1,040,491 $627,674 ($11,144,412)</t>
+          <t>Preference shares $6,823,545</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
+        <v>0.823613</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>assets, liabilities, and preferred shares, gross.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>construction of the Lethbridge One solar project until completion. At December 31, 2024, the preferred shares of LOSC are non-voting non-cumulative and redeemable at a fixed redemption value of</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>6.8e-06</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>-0.06944699999999999</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Additions</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>0.071937</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Disposal of ROU asset</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>-3.669462</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-8.44749</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.06959899999999999</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0.41131</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>0.00978</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-0.00419</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Finance expense, net</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0.081966</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Gain on sale of equipment</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>-0.000432</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>-0.019904</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Gain on debt settlement</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>-0.08447300000000001</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Loss from equity investments</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="n">
+        <v>0.137509</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0.567492</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.017237</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Acquisition expenses</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>5.801631</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Trade and other receivables</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>-0.018836</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.449187</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>-0.014988</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.050892</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ChangeInInventory</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>-0.441221</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Trade and other payables</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>1.30979</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.733026</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Customer deposits</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.305951</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>-1.579548</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>-1.146078</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cash acquired from acquisition</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0.025884</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sale of equipment</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>0.047022</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Loan receivable repayment</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>0.042341</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0.003642</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Net cash provided by investing activities</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0.089363</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.029526</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of share capital</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>1.664978</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>-0.003084</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>-0.059134</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Proceeds from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.07149999999999999</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Proceeds from loans and borrowings</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.199545</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Repayment of debentures</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Lease payments</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-0.053386</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>-0.053181</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0.72153</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>1.823708</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>-0.768655</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0.707156</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0.816883</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.048228</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Cash, end of the year $</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.048228</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.7553840000000001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Net loss ($3,669,462)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>-8.945338</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization (notes 9, 10) 69,599</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.087659</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 13) 567,492</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.459197</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Gain on sale of assets, net (432)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" s="5" t="n">
+        <v>-0.223604</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Loss from equity investments (note 8) 137,509</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>0.006241</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Shares issued for services (note 13) 30,000</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Changes in foreign exchange 9,780</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Reverse takeover expense (note 4) -</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" s="5" t="n">
+        <v>6.436937</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital (note 21) 1,413,556</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>-0.01205</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Non-cash items</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Cash flows used in operating activities (1,441,958)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
+        <v>-2.030958</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Repayment of mortgage (note 12) -</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="n">
+        <v>-0.905097</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of debenture (note 14) -</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of promissory note (note 14) 278,000</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Proceeds from private placements, net (note 13) 496,916</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Repurchase of common shares (note 13) -</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Lease payments (note 9) (53,386)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" s="5" t="n">
+        <v>-0.059482</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Repayment of shareholder loans -</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>-0.010965</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital (note 21) (139,093)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" s="5" t="n">
+        <v>0.138445</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cash flows from (used) in financing activities 582,437</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>-0.7370989999999999</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Sale of assets (note 10) 47,022</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Development costs -</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>-0.498214</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sale of development properties, net of transaction costs -</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" s="5" t="n">
+        <v>0.9981989999999999</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Investment in associate (note 8) -</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
+        <v>-0.225</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Cash received in asset acquisition (note 4) -</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>0.06313100000000001</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Loan receivable repayments (note 7) 42,341</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" s="5" t="n">
+        <v>0.299284</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Additions to property, plant and equipment (note 10) -</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>-0.004867</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Change in restricted cash -</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Net change in non-cash working capital (note 21) 1,503</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>-0.052675</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Cash flows from investing activities 90,866</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>2.274858</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Net change in cash and cash equivalents (768,655)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="n">
+        <v>-0.493199</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, beginning of period 816,883</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>1.310082</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents, end of period $48,228</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n">
+        <v>0.816883</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Interest paid on loans and borrowings, net $-</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" s="5" t="n">
+        <v>0.041494</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Going concern</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>The Company has not yet generated  sufficient revenue from the development  of  its solar power generation assets to provide positive cash flow from operating activities and has incurred losses of</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" s="5" t="n">
+        <v>3.7e-06</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Going concern</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>million for year ended December 31, 2024, and a loss of $8.9 million for the year ended December</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Going concern</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>beyond. Subsequent to December 31, 2024, the Company raised $2,052,320 by issuing shares and exercise of warrants, to reduce the Company’s debt and fund operations, see note</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" s="5" t="n">
+        <v>2.2e-05</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Going concern</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>These consolidated financial statements were approved by the Board of Directors on April 30,</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Revenue 16 $</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>0.5665829999999999</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Accounting and audit</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" s="5" t="n">
+        <v>0.422909</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>0.416644</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>0.335661</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>0.44338</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization 11,12,13</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>0.06959899999999999</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>0.41131</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Filing and transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n">
+        <v>0.033828</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>0.045987</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>0.050046</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>0.061207</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="n">
+        <v>0.06866800000000001</v>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>0.01354</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>0.123981</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.169571</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Management and director fees 16</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>0.9275</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>0.6617499999999999</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Marketing and promotion</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="n">
+        <v>1.101957</v>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>0.322</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>0.029568</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>0.051058</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>0.042334</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Salaries</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" s="5" t="n">
+        <v>0.182878</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Share-based payments 19</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" s="5" t="n">
+        <v>0.567492</v>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>0.017237</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>0.022109</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>0.033742</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>4.018086</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>2.66827</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>-3.451503</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>-2.66827</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Finance expense, net 20</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" s="5" t="n">
+        <v>-0.084166</v>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>-0.081966</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Gain (loss) on sale of equipment</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" s="5" t="n">
+        <v>-0.003591</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>0.019904</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Gain on debt settlement 18</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>0.08447300000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Acquisition expense 4</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>AcquisitionExpense</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>-5.801631</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Share in loss of joint venture and associate 9</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" s="5" t="n">
+        <v>-0.137509</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Loss before taxes</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" s="5" t="n">
+        <v>-3.676769</v>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>-8.44749</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Income tax recovery</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>0.007307</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>-3.669462</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>-8.44749</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>-1.2e-07</v>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>-1.9e-07</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>30.299073</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>44.151198</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>20.  NET FINANCE EXPENSE</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Interest on loans and borrowings $</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" s="5" t="n">
+        <v>0.07660699999999999</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>0.08368200000000001</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>20.  NET FINANCE EXPENSE</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Interest on lease liabilities (Note 11)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" s="5" t="n">
+        <v>0.007609</v>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>0.012507</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>20.  NET FINANCE EXPENSE</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Bank fees and other</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" s="5" t="n">
+        <v>0.031595</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>0.006507</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>20.  NET FINANCE EXPENSE</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Interest revenue (Note 10)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>-0.031645</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>-0.02073</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>20.  NET FINANCE EXPENSE</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>20.  NET FINANCE EXPENSE total</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" s="5" t="n">
+        <v>0.084166</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>0.081966</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Revenue (note 14) $566,583</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" s="5" t="n">
+        <v>0.401364</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>General and administrative (note 15) 3,380,995</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>2.569864</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 13) 567,492</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" s="5" t="n">
+        <v>0.459197</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization (notes 9, 10) 69,599</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>0.087659</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Share in loss of joint venture and associate (note 8) 137,509</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" s="5" t="n">
+        <v>0.006241</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Operating loss (3,589,012)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" s="5" t="n">
+        <v>-2.721597</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Reverse takeover expense (note 4) -</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="5" t="n">
+        <v>-6.436937</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>(Loss) gain on sale of assets (note 10) (3,591)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" s="5" t="n">
+        <v>0.223604</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Finance expense, net (note 17) (84,166)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" s="5" t="n">
+        <v>-0.035018</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Loss before income tax (3,676,769)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" s="5" t="n">
+        <v>-8.969948</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Income tax recovery (note 16) 7,307</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="n">
+        <v>0.02461</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss ($3,669,462)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" s="5" t="n">
+        <v>-8.945338</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Net loss per share attributable to shareholders (note</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" s="5" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Basic and diluted, net loss per share ($0.12)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>-3.6e-07</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2024 $10,085,997 $1,040,491 $627,674 ($11,144,412)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
         <v>0.60975</v>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Loss for the period - - - (3,669,462)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" s="5" t="n">
+        <v>-3.669462</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Shares issued for services (note 13) 30,000 - - -</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Shares issued in private placement, net (note 13) 496,916 - - -</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" s="5" t="n">
+        <v>0.496916</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Expiry of warrants (note 13) - (990,000) 990,000 -</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 13) - - 567,492 -</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" s="5" t="n">
+        <v>0.567492</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants     Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2024 $10,612,913 $50,491 $2,185,166 ($14,813,874)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>-1.965304</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2023 $4,578,012 $50,491 $254,277 ($2,199,074)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>2.683706</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Loss for the period - - - (8,945,338)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" s="5" t="n">
+        <v>-8.945338</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Repurchase and cancellation of shares (note 13) (104,200) - (95,800) -</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Shares and warrants issued pursuant to reverse 5,462,185 990,000 - -</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>6.452185</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>takeover (note</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>1.3e-05</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Shares issued for services (note 13) 150,000 - 10,000 -</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 13) - - 459,197 -</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
+        <v>0.459197</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Share Capital    Warrants   d Surplus           Deficit         Total</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 $10,085,997 $1,040,491 $627,674 ($11,144,412)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="5" t="n">
+        <v>0.60975</v>
+      </c>
+      <c r="F216" t="inlineStr">
         <is>
           <t>-</t>
         </is>
